--- a/Documentation/WAAM_Robot_Config/Installation_BOM.xlsx
+++ b/Documentation/WAAM_Robot_Config/Installation_BOM.xlsx
@@ -3,24 +3,35 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD713247-F5EE-47F2-8871-09C3124C4F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B017D35B-58FA-434D-8DF3-62B8A016D37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7245" yWindow="3720" windowWidth="18555" windowHeight="13095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
   <si>
     <t>Item</t>
   </si>
@@ -46,9 +57,6 @@
     <t>Pack of 25</t>
   </si>
   <si>
-    <t>$11.62</t>
-  </si>
-  <si>
     <t>Dia: 6 mm, Length: 20 mm, Material: 52100 Alloy Steel, Standards: DIN 6325-m6, ISO 8734</t>
   </si>
   <si>
@@ -68,13 +76,220 @@
   </si>
   <si>
     <t>https://www.mcmaster.com/91595A452/</t>
+  </si>
+  <si>
+    <t>89155K16</t>
+  </si>
+  <si>
+    <t>Aluminum Sheet, 6061-T651</t>
+  </si>
+  <si>
+    <t>Each</t>
+  </si>
+  <si>
+    <t>Size: 12" x 12" x 1"; Yield Str: 35,000 psi; Specs: ASTM B209; Cert: Material Cert</t>
+  </si>
+  <si>
+    <t>Oversized Thickness, Easy to Machine/Weld,</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/89155K16-89155K741/</t>
+  </si>
+  <si>
+    <t>4976N41</t>
+  </si>
+  <si>
+    <t>T-Slot Double Nut, End-Feed</t>
+  </si>
+  <si>
+    <t>Pack of 10</t>
+  </si>
+  <si>
+    <t>For Rail: 25 mm; Thread: M6; Material: Zinc-Plated Steel; Installation: End Feed</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/4976N41/</t>
+  </si>
+  <si>
+    <t>Offset mounting hole, stronger connection</t>
+  </si>
+  <si>
+    <t>5278N52</t>
+  </si>
+  <si>
+    <t>T-Slot Nut, Self-Aligning, End-Feed</t>
+  </si>
+  <si>
+    <t>Pack of 4</t>
+  </si>
+  <si>
+    <t>For Rail: 1" &amp; 25 mm; Thread: M6; Material: Zinc-Plated Steel; Feature: Self-Aligning</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/5278N52/</t>
+  </si>
+  <si>
+    <t>Stronger connection, Centered mounting hole</t>
+  </si>
+  <si>
+    <t>93070A156</t>
+  </si>
+  <si>
+    <t>Low-Profile Socket Head Screw, M6×45 mm</t>
+  </si>
+  <si>
+    <t>Material: Alloy Steel (Cl 8.8); Head Ht: 4 mm; Thread Pitch: 1 mm; Spec: DIN 7984</t>
+  </si>
+  <si>
+    <t>Fits tight spaces, partially threaded</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/93070A156/</t>
+  </si>
+  <si>
+    <t>91455A120</t>
+  </si>
+  <si>
+    <t>Flat Washer, General Purpose, M6</t>
+  </si>
+  <si>
+    <t>Pack of 100</t>
+  </si>
+  <si>
+    <t>Material: Zinc-Plated Steel; ID: 6.4 mm; OD: 12.0 mm; Spec: DIN 125, ISO 7089; Class: 8.8</t>
+  </si>
+  <si>
+    <t>Medium Strength Rating, Common for moisture exposure</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91455A120/</t>
+  </si>
+  <si>
+    <t>91290A330</t>
+  </si>
+  <si>
+    <t>Socket Head Screw, Black-Oxide, M6×25 mm</t>
+  </si>
+  <si>
+    <t>Pack of 50</t>
+  </si>
+  <si>
+    <t>Material: Alloy Steel (Cl 12.9); TS: 170,000 psi; Threading: Fully; Spec: DIN 912, ISO 4762; COO: USA</t>
+  </si>
+  <si>
+    <t>Highest strength class, mild corrosion resistance (dry)</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/91290A330/</t>
+  </si>
+  <si>
+    <t>90576A115</t>
+  </si>
+  <si>
+    <t>Nylon-Insert Locknut, M6</t>
+  </si>
+  <si>
+    <t>Material: Zinc-Plated Steel (Cl 8); Thread: M6×1 mm; H: 6 mm; Spec: DIN 985, ISO 10511</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/90576A115/</t>
+  </si>
+  <si>
+    <t>Vibration resistant, reusable, Max Temp 220 F</t>
+  </si>
+  <si>
+    <t>High-Strength Nylon-Insert Locknut, M12</t>
+  </si>
+  <si>
+    <t>98688A177</t>
+  </si>
+  <si>
+    <t>Undersized Flat Washer, General Purpose</t>
+  </si>
+  <si>
+    <t>For Screw: M12; ID: 13.0 mm; OD: 20.0 mm; Material: Zinc-Plated Steel; Spec: DIN 433; Class: 8.8</t>
+  </si>
+  <si>
+    <t>For narrow-head screws, Medium Strength</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/98688A177/</t>
+  </si>
+  <si>
+    <t>94645A229</t>
+  </si>
+  <si>
+    <t>Material: Zinc-Plated Steel (Cl 10); Thread: M12×1.5 mm (Fine); H: 12 mm; Spec: DIN 985, ISO 10511</t>
+  </si>
+  <si>
+    <t>High Strength, Vibration Resistant, Max Temp 220 F</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/94645A229/</t>
+  </si>
+  <si>
+    <t>90854A823</t>
+  </si>
+  <si>
+    <t>Hex Head Screw, Zinc Yellow-Chromate, M12×70 mm</t>
+  </si>
+  <si>
+    <t>Pack of 5</t>
+  </si>
+  <si>
+    <t>Material: Steel (Cl 10.9); Thread: M12×1.5 mm (Fine); TS: 150,000 psi; Spec: DIN 960</t>
+  </si>
+  <si>
+    <t>High-stress applications, partially threaded, good corrosion resistance</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/90854A823/</t>
+  </si>
+  <si>
+    <t>6575N411</t>
+  </si>
+  <si>
+    <t>T-Slot Rail, Double Six Slot, Solid</t>
+  </si>
+  <si>
+    <t>Size: 50mm×25mm; Material: 6560 Aluminum, Anodized; COO: USA; Feature: Solid</t>
+  </si>
+  <si>
+    <t>Smooth, Stronger than hollow, Price is per cm</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/6575N411/</t>
+  </si>
+  <si>
+    <t>60cm, $0.37 per cm</t>
+  </si>
+  <si>
+    <t>4844N114</t>
+  </si>
+  <si>
+    <t>T-Slot Corner Bracket, Extended</t>
+  </si>
+  <si>
+    <t>Material: Anodized 6063 Alum.; For Rail Ht: 50 mm; Angle: 90?; Fasteners: Included (8 x M6)</t>
+  </si>
+  <si>
+    <t>Stronger connection, No rail machining req'd, Made in USA</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/4844N114/</t>
+  </si>
+  <si>
+    <t>Sum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +311,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -105,7 +327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -114,31 +336,114 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -146,21 +451,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -168,10 +515,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <b val="0"/>
@@ -189,30 +533,584 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
         </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
+        <right style="thin">
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -229,19 +1127,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3717EEBB-595A-4C4D-BA17-B324B4C58FF2}" name="Table2" displayName="Table2" ref="A1:J3" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="2" tableBorderDxfId="3">
-  <autoFilter ref="A1:J3" xr:uid="{3717EEBB-595A-4C4D-BA17-B324B4C58FF2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3717EEBB-595A-4C4D-BA17-B324B4C58FF2}" name="Table2" displayName="Table2" ref="A1:J15" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J15" xr:uid="{3717EEBB-595A-4C4D-BA17-B324B4C58FF2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1BABA2C7-9DBD-4A35-830F-A523DEB06B0B}" name="Item"/>
-    <tableColumn id="2" xr3:uid="{61865491-C6D3-457E-8F7F-CA47E45CD155}" name="Part Number"/>
-    <tableColumn id="3" xr3:uid="{106FB5A6-C2B9-4A54-AF8F-BCD76F5978AD}" name="Description"/>
-    <tableColumn id="4" xr3:uid="{BED5EC71-ADC1-4DEB-B83D-0D0E8A9CC4F1}" name="Quantity"/>
-    <tableColumn id="5" xr3:uid="{BBEAD3CC-7538-4E2E-AC5E-074230B36341}" name="Unit"/>
-    <tableColumn id="6" xr3:uid="{5088C195-DD3D-45A0-AB9B-8C43A394545A}" name="Price"/>
-    <tableColumn id="7" xr3:uid="{7CFEB62F-F83E-4BEB-8693-2D5CCD8A73FE}" name="Cost"/>
-    <tableColumn id="8" xr3:uid="{6378D3EE-F125-4661-9122-B4B8400C8D4B}" name="Key Specs"/>
-    <tableColumn id="11" xr3:uid="{1B7F7124-5631-4D15-BE46-889D438D76D6}" name="Link"/>
-    <tableColumn id="10" xr3:uid="{D1E27D60-91B4-4920-B083-158635497006}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{1BABA2C7-9DBD-4A35-830F-A523DEB06B0B}" name="Item" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{61865491-C6D3-457E-8F7F-CA47E45CD155}" name="Part Number" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{106FB5A6-C2B9-4A54-AF8F-BCD76F5978AD}" name="Description" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{BED5EC71-ADC1-4DEB-B83D-0D0E8A9CC4F1}" name="Quantity" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{BBEAD3CC-7538-4E2E-AC5E-074230B36341}" name="Unit" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{5088C195-DD3D-45A0-AB9B-8C43A394545A}" name="Price" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{7CFEB62F-F83E-4BEB-8693-2D5CCD8A73FE}" name="Cost" dataDxfId="7" totalsRowDxfId="6">
+      <calculatedColumnFormula>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{6378D3EE-F125-4661-9122-B4B8400C8D4B}" name="Key Specs" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{1B7F7124-5631-4D15-BE46-889D438D76D6}" name="Link" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{D1E27D60-91B4-4920-B083-158635497006}" name="Note" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -544,91 +1444,518 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="13.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="15" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="84.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="49.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="80.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="49.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="63.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="7">
+        <v>11.62</v>
+      </c>
+      <c r="G2" s="7">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>11.62</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="12">
+        <v>112.08</v>
+      </c>
+      <c r="G3" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>224.16</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="12">
+        <v>8.09</v>
+      </c>
+      <c r="G4" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>16.18</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="8">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="12">
+        <v>5.09</v>
+      </c>
+      <c r="G5" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>20.36</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="8">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="12">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="G6" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>18.920000000000002</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="12">
+        <v>5.65</v>
+      </c>
+      <c r="G7" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>5.65</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="12">
+        <v>10.58</v>
+      </c>
+      <c r="G8" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>10.58</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="12">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="G9" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="12">
+        <v>10.29</v>
+      </c>
+      <c r="G10" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>10.29</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="12">
+        <v>11.13</v>
+      </c>
+      <c r="G11" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>11.13</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="12">
+        <v>14.5</v>
+      </c>
+      <c r="G12" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>29</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
         <v>12</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="B13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="8">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="E13" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="12">
+        <v>22</v>
+      </c>
+      <c r="G13" s="12">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>88</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
+      <c r="B14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="15">
+        <v>8</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="16">
+        <v>17.38</v>
+      </c>
+      <c r="G14" s="16">
+        <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
+        <v>139.04</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>15</v>
-      </c>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16">
+        <f>SUBTOTAL(109,G2:G14)</f>
+        <v>589.69999999999993</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{30E68DFC-1F1F-4891-A51D-CB9F2D171FC5}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{4C087192-EB66-4D6D-85B6-408C4E17B9E6}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{8710F23F-9A78-4635-8968-7264415DEF0F}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{13B796C9-EC98-4622-81D4-62136E79FA12}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{F578767B-A640-4B66-A183-D9C185CAC315}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{7B5E877A-A5DD-4DD7-89C8-E40E2091ABEA}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{E2A50838-8A52-4D87-9193-492795C37CB8}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{9988ED4F-9D25-43E3-A559-4B958D5D92D8}"/>
+    <hyperlink ref="I11" r:id="rId9" xr:uid="{C4D72A43-231D-49CB-8EED-895960C7DC20}"/>
+    <hyperlink ref="I10" r:id="rId10" xr:uid="{67BFF6AE-77A1-42DA-B966-4EB4AF716D6C}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{FC64A2E7-DAA1-48B9-A21B-7D25902DE7ED}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{852292D1-A76B-46D1-AAB5-2C38F2E594D6}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{B0B75BEA-DF24-496A-A39F-83C7997ABE09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>